--- a/data/trans_orig/IP1007-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136228</t>
+          <t>134991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149982</t>
+          <t>149585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287727</t>
+          <t>287291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191899</t>
+          <t>192169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403833</t>
+          <t>404308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135175</t>
+          <t>134824</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>143593</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149014</t>
+          <t>149017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281243</t>
+          <t>281189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286829</t>
+          <t>286754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>203869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412931</t>
+          <t>413218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676304</t>
+          <t>675877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>680497</t>
+          <t>680498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715706</t>
+          <t>715396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394127</t>
+          <t>1394134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401446</t>
+          <t>1401359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131573</t>
+          <t>131208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283160</t>
+          <t>284327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207458</t>
+          <t>207070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413978</t>
+          <t>414762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701920</t>
+          <t>701444</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743843</t>
+          <t>744427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1449347</t>
+          <t>1449237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454501</t>
+          <t>1454503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126474</t>
+          <t>127860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276046</t>
+          <t>275325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221211</t>
+          <t>221246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>429085</t>
+          <t>428483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200964</t>
+          <t>201708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408581</t>
+          <t>408486</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>698116</t>
+          <t>698555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>738921</t>
+          <t>739007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744216</t>
+          <t>744220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1441715</t>
+          <t>1441690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448058</t>
+          <t>1448057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1007-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4010</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4512</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152524</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>150277</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138110</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>134991</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>135362</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152524</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149585</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>427</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287291</t>
+          <t>287793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3582</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>2994</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194565</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>192169</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191581</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>633</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404308</t>
+          <t>404311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2993</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6064</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>147642</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>144280</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149018</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137293</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>134824</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>134932</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>147642</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>143593</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149017</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>457</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281189</t>
+          <t>281667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286754</t>
+          <t>286828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204307</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207124</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203869</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>579</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413218</t>
+          <t>413605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7086</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5498</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7304</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>719432</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>715614</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>721441</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679283</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675877</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680498</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>675523</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680497</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>719432</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>715396</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721444</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2096</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394134</t>
+          <t>1393826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401359</t>
+          <t>1401790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,87 +2674,87 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5342</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135495</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>131208</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131049</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152411</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148997</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>392</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284327</t>
+          <t>284330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3230</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3837</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2620</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209732</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>207070</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>207194</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>555</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414762</t>
+          <t>413545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3739</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5484</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>747455</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>744403</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705464</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>701444</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701306</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>747455</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>744427</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2081</t>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1449237</t>
+          <t>1449308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5847</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6970</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5813</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6458</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>132544</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>127860</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>126737</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,79%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>381</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275325</t>
+          <t>275970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,92 +4959,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3322</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3113</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>223733</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>221037</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>223733</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>221246</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>665</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428483</t>
+          <t>428485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4385</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4028</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4567</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4670</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204409</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201351</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204409</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201708</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>569</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408486</t>
+          <t>408589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5837</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742891</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>739520</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744222</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703208</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698555</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698551</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742891</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739007</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744220</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2122</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1441690</t>
+          <t>1441294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448057</t>
+          <t>1448519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
